--- a/backend/data/financials_by_company/1KBX.MI.xlsx
+++ b/backend/data/financials_by_company/1KBX.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,216 +692,124 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-34320000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1396000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>445000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>512000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3646000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1264000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>752000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-72000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>542680000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>445000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7010000000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="W2" t="n">
-        <v>445000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>445000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>445000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-32000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>477000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>477000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>168000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>645000000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>-138000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-72000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>11502000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>2073000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>873000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3364000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>649000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>360000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>260000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>73000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>155000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>155000000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>4237000000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3646000000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7883000000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7883000000</v>
-      </c>
+        <v>-241000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>11502000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4318000</v>
+        <v>-9744050</v>
       </c>
       <c r="C3" t="n">
-        <v>0.254</v>
+        <v>0.265</v>
       </c>
       <c r="D3" t="n">
-        <v>1493000000</v>
+        <v>1080767000</v>
       </c>
       <c r="E3" t="n">
-        <v>-17000000</v>
+        <v>-36770000</v>
       </c>
       <c r="F3" t="n">
-        <v>-17000000</v>
+        <v>-36770000</v>
       </c>
       <c r="G3" t="n">
-        <v>553000000</v>
+        <v>489276000</v>
       </c>
       <c r="H3" t="n">
-        <v>602000000</v>
+        <v>304678000</v>
       </c>
       <c r="I3" t="n">
-        <v>3910000000</v>
+        <v>3629354000</v>
       </c>
       <c r="J3" t="n">
-        <v>1476000000</v>
+        <v>1043997000</v>
       </c>
       <c r="K3" t="n">
-        <v>874000000</v>
+        <v>739319000</v>
       </c>
       <c r="L3" t="n">
-        <v>-80000000</v>
+        <v>18866000</v>
       </c>
       <c r="M3" t="n">
-        <v>101000000</v>
+        <v>50551000</v>
       </c>
       <c r="N3" t="n">
-        <v>32000000</v>
+        <v>49131000</v>
       </c>
       <c r="O3" t="n">
-        <v>565682000</v>
+        <v>516301950</v>
       </c>
       <c r="P3" t="n">
-        <v>553000000</v>
+        <v>489276000</v>
       </c>
       <c r="Q3" t="n">
-        <v>7102000000</v>
+        <v>6415067000</v>
       </c>
       <c r="R3" t="n">
-        <v>21243000</v>
+        <v>19298000</v>
       </c>
       <c r="S3" t="n">
         <v>161200000</v>
@@ -910,162 +818,162 @@
         <v>161200000</v>
       </c>
       <c r="U3" t="n">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="V3" t="n">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="W3" t="n">
-        <v>553000000</v>
+        <v>489276000</v>
       </c>
       <c r="X3" t="n">
-        <v>553000000</v>
+        <v>489276000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>553000000</v>
+        <v>489276000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-23000000</v>
+        <v>-16979000</v>
       </c>
       <c r="AB3" t="n">
-        <v>576000000</v>
+        <v>506255000</v>
       </c>
       <c r="AC3" t="n">
-        <v>576000000</v>
+        <v>506255000</v>
       </c>
       <c r="AD3" t="n">
-        <v>197000000</v>
+        <v>182513000</v>
       </c>
       <c r="AE3" t="n">
-        <v>773000000</v>
+        <v>688768000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2522000</v>
+        <v>5807000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-23000000</v>
+        <v>-28194000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4000000</v>
+        <v>-1475000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>9997000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19000000</v>
+        <v>19672000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-80000000</v>
+        <v>18866000</v>
       </c>
       <c r="AL3" t="n">
-        <v>11000000</v>
+        <v>-20286000</v>
       </c>
       <c r="AM3" t="n">
-        <v>101000000</v>
+        <v>50551000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32000000</v>
+        <v>49131000</v>
       </c>
       <c r="AO3" t="n">
-        <v>824000000</v>
+        <v>734673000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3192000000</v>
+        <v>2785713000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>655000000</v>
+        <v>426014000</v>
       </c>
       <c r="AR3" t="n">
-        <v>332000000</v>
+        <v>304678000</v>
       </c>
       <c r="AS3" t="n">
-        <v>90000000</v>
+        <v>69704000</v>
       </c>
       <c r="AT3" t="n">
-        <v>242000000</v>
+        <v>234974000</v>
       </c>
       <c r="AU3" t="n">
-        <v>62000000</v>
+        <v>53647000</v>
       </c>
       <c r="AV3" t="n">
-        <v>97000000</v>
+        <v>124144000</v>
       </c>
       <c r="AW3" t="n">
-        <v>97000000</v>
+        <v>124144000</v>
       </c>
       <c r="AX3" t="n">
-        <v>21243000</v>
+        <v>19298000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4016000000</v>
+        <v>3520386000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3910000000</v>
+        <v>3629354000</v>
       </c>
       <c r="BA3" t="n">
-        <v>7926000000</v>
+        <v>7149740000</v>
       </c>
       <c r="BB3" t="n">
-        <v>7926000000</v>
+        <v>7149740000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-9744050</v>
+        <v>-4318000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.265</v>
+        <v>0.254</v>
       </c>
       <c r="D4" t="n">
-        <v>1080767000</v>
+        <v>1493000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-36770000</v>
+        <v>-17000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-36770000</v>
+        <v>-17000000</v>
       </c>
       <c r="G4" t="n">
-        <v>489276000</v>
+        <v>553000000</v>
       </c>
       <c r="H4" t="n">
-        <v>304678000</v>
+        <v>602000000</v>
       </c>
       <c r="I4" t="n">
-        <v>3629354000</v>
+        <v>3910000000</v>
       </c>
       <c r="J4" t="n">
-        <v>1043997000</v>
+        <v>1476000000</v>
       </c>
       <c r="K4" t="n">
-        <v>739319000</v>
+        <v>874000000</v>
       </c>
       <c r="L4" t="n">
-        <v>18866000</v>
+        <v>-80000000</v>
       </c>
       <c r="M4" t="n">
-        <v>50551000</v>
+        <v>101000000</v>
       </c>
       <c r="N4" t="n">
-        <v>49131000</v>
+        <v>32000000</v>
       </c>
       <c r="O4" t="n">
-        <v>516301950</v>
+        <v>565682000</v>
       </c>
       <c r="P4" t="n">
-        <v>489276000</v>
+        <v>553000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6415067000</v>
+        <v>7102000000</v>
       </c>
       <c r="R4" t="n">
-        <v>19298000</v>
+        <v>21243000</v>
       </c>
       <c r="S4" t="n">
         <v>161200000</v>
@@ -1074,163 +982,161 @@
         <v>161200000</v>
       </c>
       <c r="U4" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="V4" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="W4" t="n">
-        <v>489276000</v>
+        <v>553000000</v>
       </c>
       <c r="X4" t="n">
-        <v>489276000</v>
+        <v>553000000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>489276000</v>
+        <v>553000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-16979000</v>
+        <v>-23000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>506255000</v>
+        <v>576000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>506255000</v>
+        <v>576000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>182513000</v>
+        <v>197000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>688768000</v>
+        <v>773000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5807000</v>
+        <v>2522000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-28194000</v>
+        <v>-23000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1475000</v>
+        <v>4000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>9997000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19672000</v>
+        <v>19000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18866000</v>
+        <v>-80000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-20286000</v>
+        <v>11000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>50551000</v>
+        <v>101000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>49131000</v>
+        <v>32000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>734673000</v>
+        <v>824000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2785713000</v>
+        <v>3192000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>426014000</v>
+        <v>655000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>304678000</v>
+        <v>332000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>69704000</v>
+        <v>90000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>234974000</v>
+        <v>242000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>53647000</v>
+        <v>62000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>124144000</v>
+        <v>97000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>124144000</v>
+        <v>97000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>19298000</v>
+        <v>21243000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3520386000</v>
+        <v>4016000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3629354000</v>
+        <v>3910000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>7149740000</v>
+        <v>7926000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>7149740000</v>
+        <v>7926000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>933595</v>
+        <v>-34320000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.265</v>
+        <v>0.26</v>
       </c>
       <c r="D5" t="n">
-        <v>1223600000</v>
+        <v>1244000000</v>
       </c>
       <c r="E5" t="n">
-        <v>3523000</v>
+        <v>-132000000</v>
       </c>
       <c r="F5" t="n">
-        <v>3523000</v>
+        <v>-132000000</v>
       </c>
       <c r="G5" t="n">
-        <v>621310000</v>
+        <v>445000000</v>
       </c>
       <c r="H5" t="n">
-        <v>290438000</v>
+        <v>360000000</v>
       </c>
       <c r="I5" t="n">
-        <v>3254504000</v>
+        <v>3646000000</v>
       </c>
       <c r="J5" t="n">
-        <v>1227123000</v>
+        <v>1112000000</v>
       </c>
       <c r="K5" t="n">
-        <v>936685000</v>
+        <v>752000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-39428000</v>
+        <v>-72000000</v>
       </c>
       <c r="M5" t="n">
-        <v>55872000</v>
+        <v>107000000</v>
       </c>
       <c r="N5" t="n">
-        <v>16203000</v>
+        <v>60000000</v>
       </c>
       <c r="O5" t="n">
-        <v>618720595</v>
+        <v>542680000</v>
       </c>
       <c r="P5" t="n">
-        <v>621310000</v>
+        <v>445000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>5803410000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>11502000</v>
-      </c>
+        <v>6967000000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>161200000</v>
       </c>
@@ -1238,106 +1144,258 @@
         <v>161200000</v>
       </c>
       <c r="U5" t="n">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="V5" t="n">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="W5" t="n">
-        <v>621310000</v>
+        <v>445000000</v>
       </c>
       <c r="X5" t="n">
-        <v>621310000</v>
+        <v>445000000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>621310000</v>
+        <v>445000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-26058000</v>
+        <v>-32000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>647368000</v>
+        <v>477000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>647368000</v>
+        <v>477000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>233445000</v>
+        <v>168000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>880813000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2073000</v>
-      </c>
+        <v>645000000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>-3093000</v>
+        <v>-136000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-25433000</v>
+        <v>38000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>20115000</v>
+        <v>65000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8411000</v>
+        <v>33000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-39428000</v>
+        <v>-72000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-241000</v>
+        <v>25000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>55872000</v>
+        <v>107000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>16203000</v>
+        <v>60000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>902230000</v>
+        <v>916000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2548906000</v>
+        <v>3321000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>397144000</v>
+        <v>606000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>282027000</v>
+        <v>360000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>56516000</v>
+        <v>100000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>225511000</v>
+        <v>260000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>48249000</v>
+        <v>73000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>131555000</v>
+        <v>155000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>131555000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11502000</v>
-      </c>
+        <v>155000000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>3451136000</v>
+        <v>4237000000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3254504000</v>
+        <v>3646000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>6705640000</v>
+        <v>7883000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>6705640000</v>
+        <v>7883000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-6040000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1343000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>378000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3527000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1323000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>945000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-75000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>547960000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6895000000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>534000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-38000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>572000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>572000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>247000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>819000000</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-75000000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>922000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3368000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>586000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>378000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>115000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>263000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>167000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>167000000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>4290000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3527000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7817000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7817000000</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,205 +1761,93 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1229000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3045000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2103000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1229000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3045000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3045000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3127000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>82000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3045000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-144000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3014000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>161000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>161000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6487000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3174000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>271000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>228000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3313000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>139000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>170000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1241000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>113000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1128000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9614000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4198000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>237000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>83000000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>83000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1816000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>933000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>883000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1899000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-1875000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3774000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>234000000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>2279000000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1261000000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5416000000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>206000000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>2105000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>7514000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>25759000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>96206000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>2046113000</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>29526000</v>
+      </c>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1206000000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>407000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>151000000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>648000000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>81000000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1385000000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2352000000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>89000000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>2263000000</v>
-      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>161200000</v>
@@ -1910,206 +1856,206 @@
         <v>161200000</v>
       </c>
       <c r="D3" t="n">
-        <v>1368000000</v>
+        <v>1097560000</v>
       </c>
       <c r="E3" t="n">
-        <v>2836000000</v>
+        <v>2563085000</v>
       </c>
       <c r="F3" t="n">
-        <v>1977000000</v>
+        <v>1719694000</v>
       </c>
       <c r="G3" t="n">
-        <v>1368000000</v>
+        <v>1097560000</v>
       </c>
       <c r="H3" t="n">
-        <v>2836000000</v>
+        <v>2563085000</v>
       </c>
       <c r="I3" t="n">
-        <v>2836000000</v>
+        <v>2563085000</v>
       </c>
       <c r="J3" t="n">
-        <v>2904000000</v>
+        <v>2627985000</v>
       </c>
       <c r="K3" t="n">
-        <v>68000000</v>
+        <v>64900000</v>
       </c>
       <c r="L3" t="n">
-        <v>2836000000</v>
+        <v>2563085000</v>
       </c>
       <c r="M3" t="n">
-        <v>-169000000</v>
+        <v>-124209000</v>
       </c>
       <c r="N3" t="n">
-        <v>2830000000</v>
+        <v>2512210000</v>
       </c>
       <c r="O3" t="n">
-        <v>14000000</v>
+        <v>13884000</v>
       </c>
       <c r="P3" t="n">
-        <v>161000000</v>
+        <v>161200000</v>
       </c>
       <c r="Q3" t="n">
-        <v>161000000</v>
+        <v>161200000</v>
       </c>
       <c r="R3" t="n">
-        <v>5345000000</v>
+        <v>5513574000</v>
       </c>
       <c r="S3" t="n">
-        <v>2803000000</v>
+        <v>2831010000</v>
       </c>
       <c r="T3" t="n">
-        <v>7000000</v>
+        <v>1825000</v>
       </c>
       <c r="U3" t="n">
-        <v>261000000</v>
+        <v>241371000</v>
       </c>
       <c r="V3" t="n">
-        <v>4000000</v>
+        <v>5782000</v>
       </c>
       <c r="W3" t="n">
-        <v>760000</v>
+        <v>1042000</v>
       </c>
       <c r="X3" t="n">
-        <v>133000000</v>
+        <v>188737000</v>
       </c>
       <c r="Y3" t="n">
-        <v>225000000</v>
+        <v>194192000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2542000000</v>
+        <v>2682564000</v>
       </c>
       <c r="AA3" t="n">
-        <v>121000000</v>
+        <v>15106000</v>
       </c>
       <c r="AB3" t="n">
-        <v>16000000</v>
+        <v>31122000</v>
       </c>
       <c r="AC3" t="n">
-        <v>133000000</v>
+        <v>171381000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1299000000</v>
+        <v>1407751000</v>
       </c>
       <c r="AE3" t="n">
-        <v>97000000</v>
+        <v>193797000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1202000000</v>
+        <v>1213954000</v>
       </c>
       <c r="AG3" t="n">
-        <v>8249000000</v>
+        <v>8141559000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3730000000</v>
+        <v>3739301000</v>
       </c>
       <c r="AI3" t="n">
-        <v>95000000</v>
+        <v>42745000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26000000</v>
+        <v>19499000</v>
       </c>
       <c r="AK3" t="n">
-        <v>7277000</v>
+        <v>8307000</v>
       </c>
       <c r="AL3" t="n">
-        <v>44889000</v>
+        <v>35505000</v>
       </c>
       <c r="AM3" t="n">
-        <v>73000000</v>
+        <v>144729000</v>
       </c>
       <c r="AN3" t="n">
-        <v>141000000</v>
+        <v>122822000</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>141000000</v>
+        <v>122822000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>61000000</v>
+        <v>79567000</v>
       </c>
       <c r="AR3" t="n">
-        <v>61000000</v>
+        <v>79567000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1468000000</v>
+        <v>1465525000</v>
       </c>
       <c r="AT3" t="n">
-        <v>772000000</v>
+        <v>766434000</v>
       </c>
       <c r="AU3" t="n">
-        <v>696000000</v>
+        <v>699091000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1864000000</v>
+        <v>1814451000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1731000000</v>
+        <v>-1748533000</v>
       </c>
       <c r="AX3" t="n">
-        <v>3595000000</v>
+        <v>3562984000</v>
       </c>
       <c r="AY3" t="n">
-        <v>238000000</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>233553000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2155700000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>2147000000</v>
+        <v>2155700000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1210000000</v>
+        <v>1173731000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4519000000</v>
+        <v>4402258000</v>
       </c>
       <c r="BD3" t="n">
-        <v>185000000</v>
+        <v>16097000</v>
       </c>
       <c r="BE3" t="n">
-        <v>221000000</v>
+        <v>170245000</v>
       </c>
       <c r="BF3" t="n">
-        <v>33734000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1180000</v>
-      </c>
+        <v>29948000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>9000000</v>
+        <v>17594000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1133000000</v>
+        <v>1132472000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>352000000</v>
+        <v>359126000</v>
       </c>
       <c r="BK3" t="n">
-        <v>135000000</v>
+        <v>137478000</v>
       </c>
       <c r="BL3" t="n">
-        <v>646000000</v>
+        <v>635868000</v>
       </c>
       <c r="BM3" t="n">
-        <v>77000000</v>
+        <v>69491000</v>
       </c>
       <c r="BN3" t="n">
-        <v>83000000</v>
+        <v>177403000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1359000000</v>
+        <v>1343305000</v>
       </c>
       <c r="BP3" t="n">
-        <v>1452000000</v>
+        <v>1445703000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>161000000</v>
+        <v>103116000</v>
       </c>
       <c r="BR3" t="n">
-        <v>1291000000</v>
+        <v>1342587000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>161200000</v>
@@ -2118,206 +2064,206 @@
         <v>161200000</v>
       </c>
       <c r="D4" t="n">
-        <v>1097560000</v>
+        <v>1368000000</v>
       </c>
       <c r="E4" t="n">
-        <v>2563085000</v>
+        <v>2836000000</v>
       </c>
       <c r="F4" t="n">
-        <v>1719694000</v>
+        <v>1977000000</v>
       </c>
       <c r="G4" t="n">
-        <v>1097560000</v>
+        <v>1368000000</v>
       </c>
       <c r="H4" t="n">
-        <v>2563085000</v>
+        <v>2836000000</v>
       </c>
       <c r="I4" t="n">
-        <v>2563085000</v>
+        <v>2836000000</v>
       </c>
       <c r="J4" t="n">
-        <v>2627985000</v>
+        <v>2904000000</v>
       </c>
       <c r="K4" t="n">
-        <v>64900000</v>
+        <v>68000000</v>
       </c>
       <c r="L4" t="n">
-        <v>2563085000</v>
+        <v>2836000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-124209000</v>
+        <v>-169000000</v>
       </c>
       <c r="N4" t="n">
-        <v>2512210000</v>
+        <v>2830000000</v>
       </c>
       <c r="O4" t="n">
-        <v>13884000</v>
+        <v>14000000</v>
       </c>
       <c r="P4" t="n">
-        <v>161200000</v>
+        <v>161000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>161200000</v>
+        <v>161000000</v>
       </c>
       <c r="R4" t="n">
-        <v>5513574000</v>
+        <v>5345000000</v>
       </c>
       <c r="S4" t="n">
-        <v>2831010000</v>
+        <v>2803000000</v>
       </c>
       <c r="T4" t="n">
-        <v>1825000</v>
+        <v>7000000</v>
       </c>
       <c r="U4" t="n">
-        <v>241371000</v>
+        <v>261000000</v>
       </c>
       <c r="V4" t="n">
-        <v>5782000</v>
+        <v>4000000</v>
       </c>
       <c r="W4" t="n">
-        <v>1042000</v>
+        <v>760000</v>
       </c>
       <c r="X4" t="n">
-        <v>188737000</v>
+        <v>133000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>194192000</v>
+        <v>225000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2682564000</v>
+        <v>2542000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>15106000</v>
+        <v>121000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>31122000</v>
+        <v>16000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>171381000</v>
+        <v>133000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1407751000</v>
+        <v>1299000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>193797000</v>
+        <v>97000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1213954000</v>
+        <v>1202000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8141559000</v>
+        <v>8249000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3739301000</v>
+        <v>3730000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>42745000</v>
+        <v>95000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19499000</v>
+        <v>26000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8307000</v>
+        <v>7277000</v>
       </c>
       <c r="AL4" t="n">
-        <v>35505000</v>
+        <v>44889000</v>
       </c>
       <c r="AM4" t="n">
-        <v>144729000</v>
+        <v>73000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>122822000</v>
+        <v>141000000</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>122822000</v>
+        <v>141000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>79567000</v>
+        <v>61000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>79567000</v>
+        <v>61000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1465525000</v>
+        <v>1468000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>766434000</v>
+        <v>772000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>699091000</v>
+        <v>696000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1814451000</v>
+        <v>1864000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1748533000</v>
+        <v>-1731000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3562984000</v>
+        <v>3595000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>233553000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2155700000</v>
-      </c>
+        <v>238000000</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>2155700000</v>
+        <v>2147000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1173731000</v>
+        <v>1210000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>4402258000</v>
+        <v>4519000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>16097000</v>
+        <v>185000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>170245000</v>
+        <v>221000000</v>
       </c>
       <c r="BF4" t="n">
-        <v>29948000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>33734000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1180000</v>
+      </c>
       <c r="BH4" t="n">
-        <v>17594000</v>
+        <v>9000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1132472000</v>
+        <v>1133000000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>359126000</v>
+        <v>352000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>137478000</v>
+        <v>135000000</v>
       </c>
       <c r="BL4" t="n">
-        <v>635868000</v>
+        <v>646000000</v>
       </c>
       <c r="BM4" t="n">
-        <v>69491000</v>
+        <v>77000000</v>
       </c>
       <c r="BN4" t="n">
-        <v>177403000</v>
+        <v>83000000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1343305000</v>
+        <v>1359000000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1445703000</v>
+        <v>1452000000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>103116000</v>
+        <v>161000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>1342587000</v>
+        <v>1291000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>161200000</v>
@@ -2326,201 +2272,389 @@
         <v>161200000</v>
       </c>
       <c r="D5" t="n">
-        <v>1322518000</v>
+        <v>1229000000</v>
       </c>
       <c r="E5" t="n">
-        <v>2328345000</v>
+        <v>3045000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1240290000</v>
+        <v>2103000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1322518000</v>
+        <v>1229000000</v>
       </c>
       <c r="H5" t="n">
-        <v>2328345000</v>
+        <v>3045000000</v>
       </c>
       <c r="I5" t="n">
-        <v>2328345000</v>
+        <v>3045000000</v>
       </c>
       <c r="J5" t="n">
-        <v>2425528000</v>
+        <v>3127000000</v>
       </c>
       <c r="K5" t="n">
-        <v>97183000</v>
+        <v>82000000</v>
       </c>
       <c r="L5" t="n">
-        <v>2328345000</v>
+        <v>3045000000</v>
       </c>
       <c r="M5" t="n">
-        <v>-196173000</v>
+        <v>-144000000</v>
       </c>
       <c r="N5" t="n">
-        <v>2333467000</v>
+        <v>3014000000</v>
       </c>
       <c r="O5" t="n">
-        <v>13884000</v>
+        <v>14000000</v>
       </c>
       <c r="P5" t="n">
-        <v>161200000</v>
+        <v>161000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>161200000</v>
+        <v>161000000</v>
       </c>
       <c r="R5" t="n">
-        <v>4773633000</v>
+        <v>6487000000</v>
       </c>
       <c r="S5" t="n">
-        <v>2076285000</v>
+        <v>3174000000</v>
       </c>
       <c r="T5" t="n">
-        <v>1840000</v>
+        <v>13000000</v>
       </c>
       <c r="U5" t="n">
-        <v>333730000</v>
+        <v>271000000</v>
       </c>
       <c r="V5" t="n">
-        <v>79787000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2105000</v>
-      </c>
+        <v>17000000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>134861000</v>
+        <v>90000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>227831000</v>
+        <v>228000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2697348000</v>
+        <v>3313000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>7201000</v>
+        <v>139000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>28819000</v>
+        <v>19000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>240740000</v>
+        <v>170000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1282227000</v>
+        <v>1241000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>116165000</v>
+        <v>113000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1166062000</v>
+        <v>1128000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>7199161000</v>
+        <v>9614000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3261523000</v>
+        <v>4198000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>39476000</v>
+        <v>102000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30092000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>7514000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>25759000</v>
-      </c>
+        <v>24000000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>117934000</v>
+        <v>237000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>215173000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>96206000</v>
-      </c>
+        <v>83000000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>215173000</v>
+        <v>83000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22073000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>36000000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>36000000</v>
+      </c>
       <c r="AS5" t="n">
-        <v>1005827000</v>
+        <v>1816000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>587648000</v>
+        <v>933000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>418179000</v>
+        <v>883000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1790359000</v>
+        <v>1899000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1631056000</v>
+        <v>-1875000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>3421415000</v>
+        <v>3774000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>247737000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2046113000</v>
-      </c>
+        <v>234000000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>2046113000</v>
+        <v>2279000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1127565000</v>
+        <v>1261000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>3937638000</v>
+        <v>5416000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>10596000</v>
+        <v>206000000</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>29526000</v>
-      </c>
+        <v>16000000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>19285000</v>
+        <v>10000000</v>
       </c>
       <c r="BI5" t="n">
-        <v>997113000</v>
+        <v>1206000000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>331894000</v>
+        <v>407000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>114961000</v>
+        <v>151000000</v>
       </c>
       <c r="BL5" t="n">
-        <v>550258000</v>
+        <v>648000000</v>
       </c>
       <c r="BM5" t="n">
-        <v>74985000</v>
+        <v>160000000</v>
       </c>
       <c r="BN5" t="n">
-        <v>131827000</v>
+        <v>81000000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1230273000</v>
+        <v>1385000000</v>
       </c>
       <c r="BP5" t="n">
-        <v>1444033000</v>
+        <v>2352000000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>63823000</v>
+        <v>89000000</v>
       </c>
       <c r="BR5" t="n">
-        <v>1380210000</v>
+        <v>2263000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1384000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3104000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2275000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1384000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3104000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3104000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3180000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3104000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-313000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3242000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>161000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>161000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5703000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3081000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>267000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>121000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>191000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2622000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>174000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1212000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1092000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8883000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3986000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>198000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1720000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>868000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>852000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1815000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1889000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3704000000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>214000000</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>2254000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1236000000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4897000000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>236000000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>251000000</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1049000000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>551000000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1308000000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1882000000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1738000000</v>
       </c>
     </row>
   </sheetData>
@@ -2534,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2786,596 +2920,656 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>696000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-31000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1099000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-346000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2230000000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1283000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>922000000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>630000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-292000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-69000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-59000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-59000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1068000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1068000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-31000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1099000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-750000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>193000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>193000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>-674000000</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-680000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-113000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-118000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-199000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-228000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-228000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1042000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-204000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-38000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-56000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>115000000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>168000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>512000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>392000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>477000000</v>
-      </c>
+        <v>5650000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>85554000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>533000000</v>
+        <v>94002000</v>
       </c>
       <c r="C3" t="n">
-        <v>-56000000</v>
+        <v>-45640000</v>
       </c>
       <c r="D3" t="n">
-        <v>16000000</v>
+        <v>740220000</v>
       </c>
       <c r="E3" t="n">
-        <v>-382000000</v>
+        <v>-447552000</v>
       </c>
       <c r="F3" t="n">
-        <v>1283000000</v>
+        <v>1210739000</v>
       </c>
       <c r="G3" t="n">
-        <v>1000000</v>
+        <v>-1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1211000000</v>
+        <v>1326497000</v>
       </c>
       <c r="I3" t="n">
-        <v>-35000000</v>
+        <v>8496000</v>
       </c>
       <c r="J3" t="n">
-        <v>106000000</v>
+        <v>-124253000</v>
       </c>
       <c r="K3" t="n">
-        <v>-398000000</v>
+        <v>-160809000</v>
       </c>
       <c r="L3" t="n">
-        <v>-216000000</v>
+        <v>-419735000</v>
       </c>
       <c r="M3" t="n">
-        <v>-67000000</v>
+        <v>-31942000</v>
       </c>
       <c r="N3" t="n">
-        <v>-59000000</v>
+        <v>-298220000</v>
       </c>
       <c r="O3" t="n">
-        <v>-59000000</v>
+        <v>-298220000</v>
       </c>
       <c r="P3" t="n">
-        <v>-40000000</v>
+        <v>694580000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-40000000</v>
+        <v>694580000</v>
       </c>
       <c r="R3" t="n">
-        <v>-56000000</v>
+        <v>-45640000</v>
       </c>
       <c r="S3" t="n">
-        <v>16000000</v>
+        <v>740220000</v>
       </c>
       <c r="T3" t="n">
-        <v>-411000000</v>
+        <v>-504998000</v>
       </c>
       <c r="U3" t="n">
-        <v>-4000000</v>
+        <v>-3794000</v>
       </c>
       <c r="V3" t="n">
-        <v>22000000</v>
+        <v>41212000</v>
       </c>
       <c r="W3" t="n">
-        <v>45000000</v>
+        <v>83117000</v>
       </c>
       <c r="X3" t="n">
-        <v>45000000</v>
+        <v>83117000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7000000</v>
+        <v>-3795000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-104000000</v>
+        <v>-207890000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-104000000</v>
+        <v>-207890000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-121000000</v>
+        <v>-124725000</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-121000000</v>
+        <v>-124725000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-249000000</v>
+        <v>-292918000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12000000</v>
+        <v>29909000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-261000000</v>
+        <v>-322827000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-254000000</v>
+        <v>-227423000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>915000000</v>
+        <v>541554000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-259000000</v>
+        <v>-203550000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-500891000</v>
       </c>
       <c r="AM3" t="n">
-        <v>120000000</v>
+        <v>139832000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-120000000</v>
+        <v>-493713000</v>
       </c>
       <c r="AO3" t="n">
-        <v>45000000</v>
+        <v>57078000</v>
       </c>
       <c r="AP3" t="n">
-        <v>116852000</v>
+        <v>83240000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>197000000</v>
+        <v>182513000</v>
       </c>
       <c r="AR3" t="n">
-        <v>602000000</v>
+        <v>304678000</v>
       </c>
       <c r="AS3" t="n">
-        <v>251000000</v>
+        <v>69704000</v>
       </c>
       <c r="AT3" t="n">
-        <v>351000000</v>
+        <v>234974000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-17000000</v>
+        <v>18796000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3000000</v>
+        <v>-614000</v>
       </c>
       <c r="AW3" t="n">
-        <v>19000000</v>
+        <v>9157000</v>
       </c>
       <c r="AX3" t="n">
-        <v>576000000</v>
+        <v>506255000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>94002000</v>
+        <v>533000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-45640000</v>
+        <v>-56000000</v>
       </c>
       <c r="D4" t="n">
-        <v>740220000</v>
+        <v>16000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-447552000</v>
+        <v>-382000000</v>
       </c>
       <c r="F4" t="n">
-        <v>1210739000</v>
+        <v>1283000000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1000</v>
+        <v>1000000</v>
       </c>
       <c r="H4" t="n">
-        <v>1326497000</v>
+        <v>1211000000</v>
       </c>
       <c r="I4" t="n">
-        <v>8496000</v>
+        <v>-35000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-124253000</v>
+        <v>106000000</v>
       </c>
       <c r="K4" t="n">
-        <v>-160809000</v>
+        <v>-398000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-419735000</v>
+        <v>-216000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-31942000</v>
+        <v>-67000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-298220000</v>
+        <v>-59000000</v>
       </c>
       <c r="O4" t="n">
-        <v>-298220000</v>
+        <v>-59000000</v>
       </c>
       <c r="P4" t="n">
-        <v>694580000</v>
+        <v>-40000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>694580000</v>
+        <v>-40000000</v>
       </c>
       <c r="R4" t="n">
-        <v>-45640000</v>
+        <v>-56000000</v>
       </c>
       <c r="S4" t="n">
-        <v>740220000</v>
+        <v>16000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-504998000</v>
+        <v>-411000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3794000</v>
+        <v>-4000000</v>
       </c>
       <c r="V4" t="n">
-        <v>41212000</v>
+        <v>22000000</v>
       </c>
       <c r="W4" t="n">
-        <v>83117000</v>
+        <v>45000000</v>
       </c>
       <c r="X4" t="n">
-        <v>83117000</v>
+        <v>45000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3795000</v>
+        <v>-7000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-207890000</v>
+        <v>-104000000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-207890000</v>
+        <v>-104000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-124725000</v>
+        <v>-121000000</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-124725000</v>
+        <v>-121000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-292918000</v>
+        <v>-249000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>29909000</v>
+        <v>12000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-322827000</v>
+        <v>-261000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-227423000</v>
+        <v>-254000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>541554000</v>
+        <v>915000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-203550000</v>
+        <v>-259000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-500891000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>139832000</v>
+        <v>120000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-493713000</v>
+        <v>-120000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>57078000</v>
+        <v>45000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>83240000</v>
+        <v>116852000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>182513000</v>
+        <v>197000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>304678000</v>
+        <v>602000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>69704000</v>
+        <v>251000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>234974000</v>
+        <v>351000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>18796000</v>
+        <v>-17000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-614000</v>
+        <v>3000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>9157000</v>
+        <v>19000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>506255000</v>
+        <v>576000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>487311000</v>
+        <v>696000000</v>
       </c>
       <c r="C5" t="n">
-        <v>-1044505000</v>
+        <v>-31000000</v>
       </c>
       <c r="D5" t="n">
-        <v>47334000</v>
+        <v>1099000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-488178000</v>
+        <v>-346000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1326497000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
+        <v>2230000000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2240725000</v>
+        <v>1283000000</v>
       </c>
       <c r="I5" t="n">
-        <v>69551000</v>
+        <v>25000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-983780000</v>
+        <v>922000000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1424895000</v>
+        <v>630000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-57450000</v>
+        <v>-28000000</v>
       </c>
       <c r="M5" t="n">
-        <v>-36616000</v>
+        <v>-59000000</v>
       </c>
       <c r="N5" t="n">
-        <v>-245024000</v>
+        <v>-264000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-245024000</v>
+        <v>-264000000</v>
       </c>
       <c r="P5" t="n">
-        <v>-997171000</v>
+        <v>1068000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-997171000</v>
+        <v>1068000000</v>
       </c>
       <c r="R5" t="n">
-        <v>-1044505000</v>
+        <v>-31000000</v>
       </c>
       <c r="S5" t="n">
-        <v>47334000</v>
+        <v>1099000000</v>
       </c>
       <c r="T5" t="n">
-        <v>-534374000</v>
+        <v>-750000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1103328000</v>
+        <v>-4000000</v>
       </c>
       <c r="V5" t="n">
-        <v>8333000</v>
+        <v>47000000</v>
       </c>
       <c r="W5" t="n">
-        <v>7631000</v>
+        <v>149000000</v>
       </c>
       <c r="X5" t="n">
-        <v>11250000</v>
+        <v>193000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3619000</v>
+        <v>-44000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-82190000</v>
+        <v>-630000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>5650000</v>
+        <v>6000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-87840000</v>
+        <v>-636000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-132741000</v>
+        <v>-113000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>890000</v>
+        <v>5000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-133631000</v>
+        <v>-118000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-335407000</v>
+        <v>-199000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>19140000</v>
+        <v>29000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-354547000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>-228000000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-228000000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>975489000</v>
+        <v>1042000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-182287000</v>
+        <v>-204000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-143174000</v>
+        <v>-38000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>84821000</v>
+        <v>18000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-115111000</v>
+        <v>-56000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>20744000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>85554000</v>
-      </c>
+        <v>115000000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>233444000</v>
+        <v>168000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>290438000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>360000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>100000000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>290438000</v>
+        <v>260000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>21454000</v>
+        <v>66000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-15883000</v>
+        <v>1000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-2929000</v>
+        <v>65000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>647368000</v>
+        <v>477000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>785000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-836000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-331000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1712000000</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>2230000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-72000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-446000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1256000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-91000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-282000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-282000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-767000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-767000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-836000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-306000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-19000000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-94000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-95000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-232000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-236000000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>1116000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-181000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-68000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>247000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>378000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>115000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>263000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-48000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>572000000</v>
       </c>
     </row>
   </sheetData>
@@ -3389,7 +3583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EW2"/>
+  <dimension ref="A1:ES2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,595 +3759,575 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
       <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4170,10 +4344,8 @@
           <t>Munich</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>80809</t>
-        </is>
+      <c r="C2" t="n">
+        <v>80809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4254,7 +4426,7 @@
         <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4271,430 +4443,418 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>98.55</v>
+        <v>100.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>98.55</v>
+        <v>100.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>103.1</v>
+        <v>105.6</v>
       </c>
       <c r="AI2" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>30.241692</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>104</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>107</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16136119296</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16829280000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>106</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>106</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.045654</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>103.606</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>95.426</v>
+      </c>
+      <c r="BA2" t="n">
         <v>1.9</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="BB2" t="n">
+        <v>0.018867925</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>17418000384</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.06998</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>61441579</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.58994</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>161200000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>20.416</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>4.903017</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>552000000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>14.811</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.23673224</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1777852800</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0.65059996</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36.6171</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CA2" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CC2" t="n">
+        <v>1264999936</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>7.855</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1176000000</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>2379000064</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.717</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>7888000000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>48.907</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.06257</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.17864999</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>4188000000</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>517500000</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1116000000</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.53093</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.12487</v>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>1KBX.MI</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1781700960</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>finmb_1532771</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-3.5060043</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.03383978</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>4.673996</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.048980318</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Knorr-Bremse Aktiengesellschaft</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>Knorr-Bremse</t>
+        </is>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1743404400000</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.5999985</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>105.6 - 105.6</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
         <v>4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>98.45</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>108</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15878200320</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16265080000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>78</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>106</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>106</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>78</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.0129564</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>102.426</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>94.255</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.019279553</v>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="BH2" t="b">
+      <c r="ED2" t="n">
+        <v>22.099998</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.2833333</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>78.0 - 106.0</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>-5.9000015</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.055660393</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>23.673225</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1785425400</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1778151600</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1778151600</v>
+      </c>
+      <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="BI2" t="n">
-        <v>17063684096</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.06998</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>61441579</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.58994</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.29978</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>161200000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>20.416</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>4.8246474</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>552000000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.29963005</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1777852800</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CG2" t="n">
-        <v>1264999936</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>7.855</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1176000000</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>2379000064</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.717</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>7888000000</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>48.907</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.06257</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.17864999</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>4188000000</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>517500000</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>1116000000</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.53093</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.14909</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.12487</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>1KBX.MI</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1743404400000</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.05000305</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>103.1 - 103.1</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.2628205</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>78.0 - 106.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.070754714</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>29.963005</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1785425400</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1778151600</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1778151600</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-3.9260025</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.038330134</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>4.2450027</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.04503743</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>Knorr-Bremse Aktiengesellschaft</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1779895010</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Knorr-Bremse</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.050738763</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>finmb_1532771</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ET2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="inlineStr"/>
+      <c r="EP2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.5958277</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="ES2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
